--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9695,0.0031,0.0045,0.0109</t>
-  </si>
-  <si>
-    <t>0.0366,0.0006,0.0004,0.9891</t>
-  </si>
-  <si>
-    <t>0.6982,0.0007,0.0005,0.5363</t>
-  </si>
-  <si>
-    <t>0.1079,0.0046,0.0063,0.9558</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0008,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9897,0.0045,0.0029,0.0012</t>
-  </si>
-  <si>
-    <t>0.9967,0.0002,0.0001,0.0019</t>
-  </si>
-  <si>
-    <t>0.9913,0.0048,0.0009,0.0021</t>
-  </si>
-  <si>
-    <t>0.9933,0.0024,0.0006,0.0020</t>
-  </si>
-  <si>
-    <t>0.9924,0.0018,0.0010,0.0021</t>
-  </si>
-  <si>
-    <t>0.9980,0.0003,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.8497,0.0198,0.1681,0.0022</t>
-  </si>
-  <si>
-    <t>0.3814,0.0291,0.6687,0.0145</t>
-  </si>
-  <si>
-    <t>0.4829,0.0085,0.6015,0.0028</t>
-  </si>
-  <si>
-    <t>0.0143,0.0040,0.9860,0.0008</t>
-  </si>
-  <si>
-    <t>0.9669,0.0027,0.0210,0.0008</t>
-  </si>
-  <si>
-    <t>0.0022,0.9948,0.0025,0.0005</t>
-  </si>
-  <si>
-    <t>0.0025,0.9937,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.0277,0.9496,0.0038,0.0055</t>
-  </si>
-  <si>
-    <t>0.0199,0.9584,0.0238,0.0089</t>
-  </si>
-  <si>
-    <t>0.0027,0.9945,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.8101,0.0011,0.2536,0.0018</t>
-  </si>
-  <si>
-    <t>0.0349,0.0046,0.9629,0.0060</t>
-  </si>
-  <si>
-    <t>0.0041,0.0008,0.9943,0.0017</t>
-  </si>
-  <si>
-    <t>0.1709,0.0252,0.8278,0.0037</t>
-  </si>
-  <si>
-    <t>0.0342,0.0073,0.9704,0.0052</t>
-  </si>
-  <si>
-    <t>0.1404,0.0041,0.9165,0.0025</t>
-  </si>
-  <si>
-    <t>0.0021,0.0004,0.9971,0.0010</t>
-  </si>
-  <si>
-    <t>0.9384,0.0480,0.0146,0.0039</t>
-  </si>
-  <si>
-    <t>0.8325,0.0667,0.1229,0.0127</t>
-  </si>
-  <si>
-    <t>0.0005,0.0126,0.9978,0.0113</t>
-  </si>
-  <si>
-    <t>0.0120,0.9563,0.0792,0.0005</t>
-  </si>
-  <si>
-    <t>0.9464,0.0159,0.0161,0.0115</t>
-  </si>
-  <si>
-    <t>0.8616,0.0376,0.1132,0.0045</t>
-  </si>
-  <si>
-    <t>0.7840,0.3375,0.0038,0.0008</t>
-  </si>
-  <si>
-    <t>0.0043,0.9838,0.1857,0.0013</t>
-  </si>
-  <si>
-    <t>0.0172,0.6912,0.2664,0.0452</t>
-  </si>
-  <si>
-    <t>0.0416,0.0211,0.9179,0.0230</t>
-  </si>
-  <si>
-    <t>0.2460,0.0158,0.8017,0.0039</t>
-  </si>
-  <si>
-    <t>0.5421,0.0021,0.5000,0.0071</t>
-  </si>
-  <si>
-    <t>0.0488,0.0790,0.9383,0.0032</t>
-  </si>
-  <si>
-    <t>0.0045,0.9823,0.0044,0.0022</t>
-  </si>
-  <si>
-    <t>0.0018,0.0069,0.9915,0.0116</t>
-  </si>
-  <si>
-    <t>0.0165,0.7494,0.0137,0.7836</t>
-  </si>
-  <si>
-    <t>0.0134,0.9528,0.0278,0.0614</t>
-  </si>
-  <si>
-    <t>0.0146,0.9639,0.0745,0.0032</t>
-  </si>
-  <si>
-    <t>0.0061,0.9850,0.0817,0.0013</t>
-  </si>
-  <si>
-    <t>0.0011,0.0216,0.9957,0.0017</t>
-  </si>
-  <si>
-    <t>0.0081,0.0747,0.9824,0.0029</t>
-  </si>
-  <si>
-    <t>0.0075,0.0021,0.9876,0.0089</t>
-  </si>
-  <si>
-    <t>0.0223,0.0008,0.9880,0.0004</t>
-  </si>
-  <si>
-    <t>0.0058,0.0079,0.9902,0.0038</t>
-  </si>
-  <si>
-    <t>0.0154,0.1075,0.9505,0.0008</t>
-  </si>
-  <si>
-    <t>0.8706,0.1696,0.0139,0.0034</t>
-  </si>
-  <si>
-    <t>0.9678,0.0060,0.0107,0.0077</t>
-  </si>
-  <si>
-    <t>0.9807,0.0104,0.0028,0.0040</t>
-  </si>
-  <si>
-    <t>0.0085,0.0852,0.9815,0.0634</t>
-  </si>
-  <si>
-    <t>0.9947,0.0021,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9976,0.0005,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9894,0.0069,0.0011,0.0014</t>
-  </si>
-  <si>
-    <t>0.0084,0.8335,0.9277,0.0023</t>
-  </si>
-  <si>
-    <t>0.0063,0.0646,0.9884,0.0023</t>
-  </si>
-  <si>
-    <t>0.0011,0.0019,0.9973,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.8430,0.9756,0.0002</t>
-  </si>
-  <si>
-    <t>0.0071,0.0016,0.9935,0.0016</t>
-  </si>
-  <si>
-    <t>0.1168,0.8655,0.0228,0.0006</t>
-  </si>
-  <si>
-    <t>0.0025,0.9943,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.4988,0.0019,0.7387,0.0009</t>
-  </si>
-  <si>
-    <t>0.9260,0.0212,0.0446,0.0022</t>
-  </si>
-  <si>
-    <t>0.0020,0.0099,0.9949,0.0104</t>
-  </si>
-  <si>
-    <t>0.0022,0.9509,0.8315,0.0005</t>
-  </si>
-  <si>
-    <t>0.0091,0.9570,0.2433,0.0012</t>
-  </si>
-  <si>
-    <t>0.0011,0.9922,0.0286,0.0023</t>
-  </si>
-  <si>
-    <t>0.0008,0.9778,0.9474,0.0003</t>
-  </si>
-  <si>
-    <t>0.0014,0.0004,0.0006,0.9990</t>
-  </si>
-  <si>
-    <t>0.0017,0.0004,0.0001,0.9992</t>
-  </si>
-  <si>
-    <t>0.0055,0.0002,0.0002,0.9979</t>
-  </si>
-  <si>
-    <t>0.0092,0.0003,0.0001,0.9972</t>
-  </si>
-  <si>
-    <t>0.0044,0.0008,0.0012,0.9965</t>
-  </si>
-  <si>
-    <t>0.0057,0.0049,0.0019,0.9939</t>
-  </si>
-  <si>
-    <t>0.0032,0.9330,0.8838,0.0005</t>
-  </si>
-  <si>
-    <t>0.0021,0.7140,0.9936,0.0002</t>
-  </si>
-  <si>
-    <t>0.0172,0.8135,0.4681,0.0115</t>
-  </si>
-  <si>
-    <t>0.0044,0.9324,0.8442,0.0004</t>
-  </si>
-  <si>
-    <t>0.0016,0.8929,0.9646,0.0003</t>
-  </si>
-  <si>
-    <t>0.0034,0.9780,0.1627,0.0046</t>
-  </si>
-  <si>
-    <t>0.9951,0.0032,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9792,0.0277,0.0014,0.0007</t>
-  </si>
-  <si>
-    <t>0.9936,0.0028,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9921,0.0004,0.0002,0.0051</t>
-  </si>
-  <si>
-    <t>0.9952,0.0013,0.0007,0.0009</t>
-  </si>
-  <si>
-    <t>0.9959,0.0009,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9877,0.0052,0.0023,0.0031</t>
-  </si>
-  <si>
-    <t>0.9753,0.0269,0.0013,0.0016</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0000,0.0008</t>
-  </si>
-  <si>
-    <t>0.9962,0.0010,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9937,0.0004,0.0002,0.0043</t>
-  </si>
-  <si>
-    <t>0.9956,0.0009,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.0063,0.0012,0.9937,0.0022</t>
-  </si>
-  <si>
-    <t>0.0222,0.0108,0.9788,0.0012</t>
-  </si>
-  <si>
-    <t>0.9271,0.0009,0.0152,0.0122</t>
-  </si>
-  <si>
-    <t>0.0177,0.0011,0.9887,0.0004</t>
-  </si>
-  <si>
-    <t>0.0065,0.9900,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.0034,0.9907,0.0050,0.0015</t>
-  </si>
-  <si>
-    <t>0.0194,0.9672,0.0071,0.0038</t>
-  </si>
-  <si>
-    <t>0.0645,0.9201,0.0159,0.0031</t>
-  </si>
-  <si>
-    <t>0.0088,0.9844,0.0072,0.0012</t>
-  </si>
-  <si>
-    <t>0.0017,0.9962,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.3286,0.7738,0.0029,0.0005</t>
-  </si>
-  <si>
-    <t>0.7983,0.0459,0.1575,0.0108</t>
-  </si>
-  <si>
-    <t>0.7370,0.0027,0.3159,0.0063</t>
-  </si>
-  <si>
-    <t>0.1765,0.0484,0.7381,0.1123</t>
-  </si>
-  <si>
-    <t>0.5530,0.0265,0.4907,0.0062</t>
-  </si>
-  <si>
-    <t>0.0065,0.0259,0.0071,0.9899</t>
-  </si>
-  <si>
-    <t>0.0148,0.9805,0.0222,0.0005</t>
-  </si>
-  <si>
-    <t>0.0062,0.9759,0.0320,0.0039</t>
-  </si>
-  <si>
-    <t>0.0009,0.9955,0.0013,0.0021</t>
-  </si>
-  <si>
-    <t>0.0039,0.9850,0.2844,0.0026</t>
-  </si>
-  <si>
-    <t>0.0999,0.8940,0.0110,0.0028</t>
-  </si>
-  <si>
-    <t>0.9606,0.0370,0.0058,0.0011</t>
-  </si>
-  <si>
-    <t>0.5491,0.5036,0.0145,0.0031</t>
-  </si>
-  <si>
-    <t>0.9873,0.0040,0.0024,0.0030</t>
-  </si>
-  <si>
-    <t>0.9932,0.0004,0.0008,0.0030</t>
-  </si>
-  <si>
-    <t>0.9965,0.0013,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9914,0.0030,0.0018,0.0012</t>
-  </si>
-  <si>
-    <t>0.9967,0.0001,0.0001,0.0032</t>
-  </si>
-  <si>
-    <t>0.9868,0.0027,0.0052,0.0021</t>
-  </si>
-  <si>
-    <t>0.9943,0.0011,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.9970,0.0012,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.0011,0.9457,0.9680,0.0001</t>
-  </si>
-  <si>
-    <t>0.0053,0.3521,0.9689,0.0008</t>
-  </si>
-  <si>
-    <t>0.0033,0.0100,0.9903,0.0007</t>
-  </si>
-  <si>
-    <t>0.0046,0.0520,0.9772,0.0041</t>
-  </si>
-  <si>
-    <t>0.8626,0.0191,0.0879,0.0124</t>
-  </si>
-  <si>
-    <t>0.8762,0.0063,0.0700,0.0122</t>
-  </si>
-  <si>
-    <t>0.8483,0.0002,0.3377,0.0001</t>
-  </si>
-  <si>
-    <t>0.3220,0.0812,0.6487,0.0249</t>
-  </si>
-  <si>
-    <t>0.0349,0.0009,0.0006,0.9898</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0005,0.0001,0.9994</t>
-  </si>
-  <si>
-    <t>0.0091,0.0002,0.0002,0.9972</t>
-  </si>
-  <si>
-    <t>0.0016,0.3628,0.9802,0.0007</t>
-  </si>
-  <si>
-    <t>0.9980,0.0003,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.1545,0.8152,0.0029,0.0259</t>
-  </si>
-  <si>
-    <t>0.9862,0.0020,0.0015,0.0055</t>
-  </si>
-  <si>
-    <t>0.6642,0.3657,0.0247,0.0057</t>
-  </si>
-  <si>
-    <t>0.9927,0.0015,0.0008,0.0019</t>
-  </si>
-  <si>
-    <t>0.9452,0.0097,0.0046,0.0402</t>
-  </si>
-  <si>
-    <t>0.9964,0.0003,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.0016,0.3307,0.9379,0.0461</t>
-  </si>
-  <si>
-    <t>0.9799,0.0003,0.0007,0.0169</t>
-  </si>
-  <si>
-    <t>0.9709,0.0012,0.0051,0.0123</t>
-  </si>
-  <si>
-    <t>0.3225,0.6785,0.0562,0.0041</t>
-  </si>
-  <si>
-    <t>0.9912,0.0025,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.9364,0.0406,0.0160,0.0051</t>
-  </si>
-  <si>
-    <t>0.1434,0.8467,0.0290,0.0111</t>
-  </si>
-  <si>
-    <t>0.9057,0.0277,0.0553,0.0035</t>
-  </si>
-  <si>
-    <t>0.9471,0.0357,0.0117,0.0036</t>
-  </si>
-  <si>
-    <t>0.9742,0.0038,0.0031,0.0153</t>
-  </si>
-  <si>
-    <t>0.9946,0.0007,0.0002,0.0030</t>
-  </si>
-  <si>
-    <t>0.9965,0.0007,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9803,0.0033,0.0032,0.0084</t>
-  </si>
-  <si>
-    <t>0.9962,0.0008,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9928,0.0032,0.0005,0.0015</t>
-  </si>
-  <si>
-    <t>0.9915,0.0034,0.0021,0.0014</t>
-  </si>
-  <si>
-    <t>0.9917,0.0005,0.0003,0.0056</t>
-  </si>
-  <si>
-    <t>0.8746,0.0609,0.0004,0.0054</t>
-  </si>
-  <si>
-    <t>0.4793,0.5844,0.0175,0.0015</t>
-  </si>
-  <si>
-    <t>0.7771,0.2844,0.0138,0.0027</t>
-  </si>
-  <si>
-    <t>0.9471,0.0136,0.0305,0.0057</t>
-  </si>
-  <si>
-    <t>0.9930,0.0041,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9883,0.0067,0.0019,0.0018</t>
-  </si>
-  <si>
-    <t>0.9910,0.0032,0.0010,0.0022</t>
-  </si>
-  <si>
-    <t>0.9625,0.0295,0.0066,0.0038</t>
-  </si>
-  <si>
-    <t>0.0030,0.0100,0.9958,0.0022</t>
-  </si>
-  <si>
-    <t>0.9899,0.0061,0.0008,0.0017</t>
-  </si>
-  <si>
-    <t>0.0028,0.0013,0.9963,0.0007</t>
-  </si>
-  <si>
-    <t>0.0030,0.0173,0.9888,0.0097</t>
-  </si>
-  <si>
-    <t>0.0068,0.0009,0.9917,0.0026</t>
-  </si>
-  <si>
-    <t>0.0044,0.0492,0.9774,0.0036</t>
-  </si>
-  <si>
-    <t>0.0111,0.0163,0.9808,0.0036</t>
-  </si>
-  <si>
-    <t>0.0128,0.0005,0.9935,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.0056,0.9922,0.0143</t>
-  </si>
-  <si>
-    <t>0.2604,0.0214,0.7911,0.0100</t>
-  </si>
-  <si>
-    <t>0.1065,0.0043,0.9370,0.0015</t>
-  </si>
-  <si>
-    <t>0.0919,0.0361,0.8915,0.0069</t>
-  </si>
-  <si>
-    <t>0.4037,0.2185,0.2324,0.0045</t>
-  </si>
-  <si>
-    <t>0.4703,0.1280,0.3371,0.0059</t>
-  </si>
-  <si>
-    <t>0.9044,0.0011,0.1577,0.0003</t>
-  </si>
-  <si>
-    <t>0.1550,0.0125,0.8666,0.0117</t>
-  </si>
-  <si>
-    <t>0.8233,0.0087,0.2186,0.0065</t>
-  </si>
-  <si>
-    <t>0.1828,0.8664,0.0027,0.0012</t>
-  </si>
-  <si>
-    <t>0.0876,0.9169,0.0081,0.0019</t>
-  </si>
-  <si>
-    <t>0.9879,0.0082,0.0009,0.0012</t>
-  </si>
-  <si>
-    <t>0.9776,0.0238,0.0020,0.0014</t>
-  </si>
-  <si>
-    <t>0.8168,0.2496,0.0051,0.0032</t>
-  </si>
-  <si>
-    <t>0.9085,0.0081,0.0989,0.0005</t>
-  </si>
-  <si>
-    <t>0.9546,0.0010,0.0345,0.0016</t>
-  </si>
-  <si>
-    <t>0.9628,0.0043,0.0033,0.0146</t>
-  </si>
-  <si>
-    <t>0.7833,0.0264,0.2176,0.0148</t>
-  </si>
-  <si>
-    <t>0.8977,0.0108,0.0720,0.0113</t>
-  </si>
-  <si>
-    <t>0.0101,0.0064,0.9815,0.0255</t>
-  </si>
-  <si>
-    <t>0.0525,0.0171,0.8562,0.0687</t>
-  </si>
-  <si>
-    <t>0.1335,0.0144,0.8618,0.0063</t>
-  </si>
-  <si>
-    <t>0.7196,0.0011,0.4719,0.0008</t>
-  </si>
-  <si>
-    <t>0.0155,0.0175,0.9677,0.0078</t>
-  </si>
-  <si>
-    <t>0.9958,0.0004,0.0004,0.0018</t>
-  </si>
-  <si>
-    <t>0.9946,0.0027,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.9935,0.0018,0.0001,0.0020</t>
-  </si>
-  <si>
-    <t>0.9910,0.0059,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.9949,0.0020,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9941,0.0019,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.9960,0.0006,0.0005,0.0011</t>
-  </si>
-  <si>
-    <t>0.9949,0.0007,0.0003,0.0021</t>
-  </si>
-  <si>
-    <t>0.0023,0.1006,0.9941,0.0021</t>
-  </si>
-  <si>
-    <t>0.3804,0.4799,0.1708,0.0061</t>
-  </si>
-  <si>
-    <t>0.9359,0.0028,0.0158,0.0244</t>
-  </si>
-  <si>
-    <t>0.0073,0.0019,0.9943,0.0002</t>
-  </si>
-  <si>
-    <t>0.0034,0.0008,0.9916,0.0053</t>
-  </si>
-  <si>
-    <t>0.0334,0.1973,0.8975,0.0081</t>
-  </si>
-  <si>
-    <t>0.0013,0.0041,0.9978,0.0007</t>
-  </si>
-  <si>
-    <t>0.0043,0.0021,0.9932,0.0016</t>
-  </si>
-  <si>
-    <t>0.0014,0.0005,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0056,0.0059,0.9860,0.0025</t>
-  </si>
-  <si>
-    <t>0.0223,0.0208,0.9624,0.0133</t>
-  </si>
-  <si>
-    <t>0.6016,0.0453,0.3114,0.0513</t>
-  </si>
-  <si>
-    <t>0.3079,0.0014,0.7010,0.0144</t>
-  </si>
-  <si>
-    <t>0.9919,0.0003,0.0034,0.0003</t>
-  </si>
-  <si>
-    <t>0.9837,0.0059,0.0019,0.0050</t>
-  </si>
-  <si>
-    <t>0.9958,0.0018,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9968,0.0005,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9850,0.0069,0.0032,0.0014</t>
-  </si>
-  <si>
-    <t>0.9925,0.0005,0.0001,0.0057</t>
-  </si>
-  <si>
-    <t>0.9979,0.0008,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9964,0.0018,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9959,0.0013,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.0268,0.0588,0.9052,0.0048</t>
-  </si>
-  <si>
-    <t>0.0077,0.0129,0.9899,0.0007</t>
-  </si>
-  <si>
-    <t>0.0133,0.0374,0.9593,0.0130</t>
-  </si>
-  <si>
-    <t>0.0079,0.0078,0.9867,0.0038</t>
-  </si>
-  <si>
-    <t>0.0025,0.0007,0.9967,0.0006</t>
-  </si>
-  <si>
-    <t>0.1745,0.0085,0.7115,0.0755</t>
-  </si>
-  <si>
-    <t>0.2291,0.0342,0.7602,0.0289</t>
-  </si>
-  <si>
-    <t>0.4359,0.0243,0.2209,0.3062</t>
-  </si>
-  <si>
-    <t>0.9325,0.0024,0.0028,0.0687</t>
-  </si>
-  <si>
-    <t>0.2782,0.0050,0.0009,0.8786</t>
-  </si>
-  <si>
-    <t>0.0494,0.0008,0.0008,0.9850</t>
-  </si>
-  <si>
-    <t>0.0009,0.0002,0.0001,0.9994</t>
-  </si>
-  <si>
-    <t>0.0008,0.0002,0.0001,0.9995</t>
-  </si>
-  <si>
-    <t>0.9533,0.0018,0.0063,0.0280</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.8916,0.0084,0.0090,0.0666</t>
+  </si>
+  <si>
+    <t>0.0171,0.0003,0.0008,0.9931</t>
+  </si>
+  <si>
+    <t>0.5518,0.0028,0.0002,0.5727</t>
+  </si>
+  <si>
+    <t>0.0406,0.0034,0.0051,0.9799</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9964,0.0007,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9943,0.0010,0.0014,0.0009</t>
+  </si>
+  <si>
+    <t>0.9974,0.0002,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9952,0.0019,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9961,0.0014,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.8388,0.0109,0.1804,0.0035</t>
+  </si>
+  <si>
+    <t>0.0614,0.0344,0.9272,0.0063</t>
+  </si>
+  <si>
+    <t>0.1751,0.0392,0.8129,0.0019</t>
+  </si>
+  <si>
+    <t>0.1112,0.0253,0.9010,0.0115</t>
+  </si>
+  <si>
+    <t>0.9209,0.0044,0.0317,0.0115</t>
+  </si>
+  <si>
+    <t>0.0056,0.9899,0.0048,0.0004</t>
+  </si>
+  <si>
+    <t>0.0057,0.9883,0.0023,0.0012</t>
+  </si>
+  <si>
+    <t>0.0375,0.9489,0.0156,0.0026</t>
+  </si>
+  <si>
+    <t>0.0028,0.9918,0.0142,0.0019</t>
+  </si>
+  <si>
+    <t>0.0012,0.9966,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.8046,0.0020,0.2805,0.0029</t>
+  </si>
+  <si>
+    <t>0.8296,0.0006,0.2736,0.0004</t>
+  </si>
+  <si>
+    <t>0.0054,0.0023,0.9912,0.0066</t>
+  </si>
+  <si>
+    <t>0.4251,0.0199,0.6391,0.0017</t>
+  </si>
+  <si>
+    <t>0.5900,0.0029,0.4199,0.0136</t>
+  </si>
+  <si>
+    <t>0.0617,0.0026,0.9209,0.0277</t>
+  </si>
+  <si>
+    <t>0.0061,0.0006,0.9950,0.0009</t>
+  </si>
+  <si>
+    <t>0.4968,0.6307,0.0067,0.0022</t>
+  </si>
+  <si>
+    <t>0.0568,0.5169,0.7056,0.0059</t>
+  </si>
+  <si>
+    <t>0.0036,0.0284,0.9932,0.0048</t>
+  </si>
+  <si>
+    <t>0.0535,0.8821,0.0761,0.0011</t>
+  </si>
+  <si>
+    <t>0.9579,0.0158,0.0106,0.0074</t>
+  </si>
+  <si>
+    <t>0.9159,0.0598,0.0209,0.0099</t>
+  </si>
+  <si>
+    <t>0.5912,0.5454,0.0019,0.0006</t>
+  </si>
+  <si>
+    <t>0.0149,0.9725,0.0544,0.0048</t>
+  </si>
+  <si>
+    <t>0.0129,0.8919,0.1631,0.0115</t>
+  </si>
+  <si>
+    <t>0.0238,0.0435,0.9641,0.0169</t>
+  </si>
+  <si>
+    <t>0.0952,0.0251,0.9180,0.0073</t>
+  </si>
+  <si>
+    <t>0.1721,0.0013,0.5355,0.0696</t>
+  </si>
+  <si>
+    <t>0.0362,0.0383,0.9642,0.0018</t>
+  </si>
+  <si>
+    <t>0.0142,0.9629,0.0134,0.0011</t>
+  </si>
+  <si>
+    <t>0.0013,0.0121,0.9933,0.0062</t>
+  </si>
+  <si>
+    <t>0.1973,0.0505,0.0180,0.8497</t>
+  </si>
+  <si>
+    <t>0.0154,0.9406,0.0274,0.0973</t>
+  </si>
+  <si>
+    <t>0.0518,0.9103,0.0490,0.0068</t>
+  </si>
+  <si>
+    <t>0.0057,0.9845,0.3660,0.0007</t>
+  </si>
+  <si>
+    <t>0.0019,0.0855,0.9850,0.0045</t>
+  </si>
+  <si>
+    <t>0.0033,0.0937,0.9905,0.0011</t>
+  </si>
+  <si>
+    <t>0.0371,0.0068,0.9471,0.0233</t>
+  </si>
+  <si>
+    <t>0.0663,0.0006,0.9756,0.0002</t>
+  </si>
+  <si>
+    <t>0.0027,0.0033,0.9962,0.0013</t>
+  </si>
+  <si>
+    <t>0.0020,0.0115,0.9883,0.0047</t>
+  </si>
+  <si>
+    <t>0.9303,0.0941,0.0085,0.0015</t>
+  </si>
+  <si>
+    <t>0.9845,0.0010,0.0045,0.0029</t>
+  </si>
+  <si>
+    <t>0.9934,0.0007,0.0021,0.0008</t>
+  </si>
+  <si>
+    <t>0.0045,0.0992,0.9890,0.0145</t>
+  </si>
+  <si>
+    <t>0.9906,0.0008,0.0008,0.0054</t>
+  </si>
+  <si>
+    <t>0.9936,0.0026,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.9952,0.0036,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0016,0.7012,0.9942,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.0169,0.9952,0.0009</t>
+  </si>
+  <si>
+    <t>0.0023,0.0081,0.9964,0.0006</t>
+  </si>
+  <si>
+    <t>0.0007,0.7949,0.9923,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.0032,0.9908,0.0109</t>
+  </si>
+  <si>
+    <t>0.0208,0.9813,0.0136,0.0001</t>
+  </si>
+  <si>
+    <t>0.0059,0.9943,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8524,0.0040,0.1443,0.0065</t>
+  </si>
+  <si>
+    <t>0.9389,0.0270,0.0186,0.0058</t>
+  </si>
+  <si>
+    <t>0.0034,0.0754,0.9868,0.0079</t>
+  </si>
+  <si>
+    <t>0.0021,0.8674,0.8968,0.0007</t>
+  </si>
+  <si>
+    <t>0.0027,0.8941,0.9161,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.9940,0.0207,0.0012</t>
+  </si>
+  <si>
+    <t>0.0017,0.9828,0.6811,0.0004</t>
+  </si>
+  <si>
+    <t>0.0030,0.0001,0.0011,0.9981</t>
+  </si>
+  <si>
+    <t>0.0017,0.0012,0.0001,0.9990</t>
+  </si>
+  <si>
+    <t>0.0043,0.0001,0.0002,0.9981</t>
+  </si>
+  <si>
+    <t>0.0105,0.0012,0.0023,0.9933</t>
+  </si>
+  <si>
+    <t>0.0026,0.0020,0.0029,0.9960</t>
+  </si>
+  <si>
+    <t>0.0020,0.0016,0.0001,0.9987</t>
+  </si>
+  <si>
+    <t>0.0050,0.9496,0.6024,0.0006</t>
+  </si>
+  <si>
+    <t>0.0013,0.9456,0.9805,0.0002</t>
+  </si>
+  <si>
+    <t>0.0204,0.0833,0.8619,0.0074</t>
+  </si>
+  <si>
+    <t>0.0077,0.7271,0.8282,0.0015</t>
+  </si>
+  <si>
+    <t>0.0061,0.9326,0.7552,0.0023</t>
+  </si>
+  <si>
+    <t>0.0024,0.8651,0.8038,0.0019</t>
+  </si>
+  <si>
+    <t>0.9956,0.0021,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9954,0.0032,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9844,0.0096,0.0028,0.0018</t>
+  </si>
+  <si>
+    <t>0.9889,0.0026,0.0002,0.0034</t>
+  </si>
+  <si>
+    <t>0.9952,0.0007,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9952,0.0020,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9966,0.0019,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9942,0.0036,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9975,0.0002,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9964,0.0006,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9958,0.0006,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9926,0.0004,0.0002,0.0065</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0015,0.0003,0.9979,0.0013</t>
+  </si>
+  <si>
+    <t>0.0071,0.0019,0.9923,0.0023</t>
+  </si>
+  <si>
+    <t>0.9333,0.0041,0.0163,0.0204</t>
+  </si>
+  <si>
+    <t>0.0058,0.0016,0.9917,0.0023</t>
+  </si>
+  <si>
+    <t>0.0088,0.9854,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.0042,0.9925,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.0027,0.9924,0.0065,0.0010</t>
+  </si>
+  <si>
+    <t>0.0239,0.9703,0.0078,0.0006</t>
+  </si>
+  <si>
+    <t>0.0075,0.9844,0.0276,0.0016</t>
+  </si>
+  <si>
+    <t>0.0027,0.9944,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9224,0.1109,0.0047,0.0007</t>
+  </si>
+  <si>
+    <t>0.8856,0.0370,0.0581,0.0074</t>
+  </si>
+  <si>
+    <t>0.5833,0.0057,0.5216,0.0056</t>
+  </si>
+  <si>
+    <t>0.5687,0.0042,0.3538,0.0340</t>
+  </si>
+  <si>
+    <t>0.4757,0.0015,0.6548,0.0018</t>
+  </si>
+  <si>
+    <t>0.0329,0.1137,0.0195,0.9423</t>
+  </si>
+  <si>
+    <t>0.0100,0.9851,0.0316,0.0008</t>
+  </si>
+  <si>
+    <t>0.0205,0.9662,0.0152,0.0016</t>
+  </si>
+  <si>
+    <t>0.0012,0.9956,0.0031,0.0021</t>
+  </si>
+  <si>
+    <t>0.0052,0.9563,0.4800,0.0111</t>
+  </si>
+  <si>
+    <t>0.0288,0.9627,0.0022,0.0021</t>
+  </si>
+  <si>
+    <t>0.2023,0.8145,0.0335,0.0033</t>
+  </si>
+  <si>
+    <t>0.8786,0.1257,0.0189,0.0041</t>
+  </si>
+  <si>
+    <t>0.9973,0.0005,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9933,0.0006,0.0006,0.0028</t>
+  </si>
+  <si>
+    <t>0.9951,0.0006,0.0002,0.0021</t>
+  </si>
+  <si>
+    <t>0.9965,0.0006,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9963,0.0002,0.0001,0.0029</t>
+  </si>
+  <si>
+    <t>0.9921,0.0011,0.0037,0.0005</t>
+  </si>
+  <si>
+    <t>0.9956,0.0014,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9974,0.0005,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.7369,0.9950,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.3489,0.9733,0.0005</t>
+  </si>
+  <si>
+    <t>0.0087,0.0155,0.9788,0.0010</t>
+  </si>
+  <si>
+    <t>0.0042,0.0028,0.9930,0.0003</t>
+  </si>
+  <si>
+    <t>0.9808,0.0017,0.0095,0.0005</t>
+  </si>
+  <si>
+    <t>0.9364,0.0042,0.0327,0.0053</t>
+  </si>
+  <si>
+    <t>0.0786,0.0038,0.9458,0.0057</t>
+  </si>
+  <si>
+    <t>0.1697,0.0198,0.8464,0.0164</t>
+  </si>
+  <si>
+    <t>0.2353,0.0002,0.0004,0.9464</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0003,0.0006,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0205,0.0003,0.0002,0.9947</t>
+  </si>
+  <si>
+    <t>0.0027,0.7917,0.9487,0.0012</t>
+  </si>
+  <si>
+    <t>0.9947,0.0013,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.3434,0.6866,0.0115,0.0070</t>
+  </si>
+  <si>
+    <t>0.9793,0.0012,0.0007,0.0158</t>
+  </si>
+  <si>
+    <t>0.8351,0.2210,0.0050,0.0032</t>
+  </si>
+  <si>
+    <t>0.9922,0.0012,0.0015,0.0013</t>
+  </si>
+  <si>
+    <t>0.8864,0.0049,0.0037,0.1414</t>
+  </si>
+  <si>
+    <t>0.9950,0.0013,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.0020,0.1869,0.9446,0.0602</t>
+  </si>
+  <si>
+    <t>0.9452,0.0008,0.0013,0.0700</t>
+  </si>
+  <si>
+    <t>0.9361,0.0049,0.0213,0.0337</t>
+  </si>
+  <si>
+    <t>0.8363,0.1880,0.0199,0.0034</t>
+  </si>
+  <si>
+    <t>0.9806,0.0050,0.0053,0.0012</t>
+  </si>
+  <si>
+    <t>0.9868,0.0039,0.0032,0.0009</t>
+  </si>
+  <si>
+    <t>0.6256,0.3411,0.0274,0.0159</t>
+  </si>
+  <si>
+    <t>0.2947,0.5199,0.3856,0.0261</t>
+  </si>
+  <si>
+    <t>0.9506,0.0224,0.0228,0.0019</t>
+  </si>
+  <si>
+    <t>0.9875,0.0047,0.0017,0.0035</t>
+  </si>
+  <si>
+    <t>0.9896,0.0059,0.0010,0.0024</t>
+  </si>
+  <si>
+    <t>0.9934,0.0027,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9937,0.0008,0.0006,0.0025</t>
+  </si>
+  <si>
+    <t>0.9916,0.0018,0.0009,0.0022</t>
+  </si>
+  <si>
+    <t>0.9940,0.0029,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9964,0.0005,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9952,0.0006,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.8703,0.1708,0.0025,0.0018</t>
+  </si>
+  <si>
+    <t>0.8741,0.1733,0.0037,0.0016</t>
+  </si>
+  <si>
+    <t>0.6214,0.4489,0.0076,0.0067</t>
+  </si>
+  <si>
+    <t>0.9538,0.0093,0.0263,0.0032</t>
+  </si>
+  <si>
+    <t>0.9649,0.0364,0.0029,0.0025</t>
+  </si>
+  <si>
+    <t>0.9901,0.0053,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.9937,0.0018,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.9778,0.0115,0.0021,0.0046</t>
+  </si>
+  <si>
+    <t>0.0021,0.0179,0.9976,0.0010</t>
+  </si>
+  <si>
+    <t>0.9568,0.0301,0.0035,0.0082</t>
+  </si>
+  <si>
+    <t>0.0258,0.0022,0.9807,0.0004</t>
+  </si>
+  <si>
+    <t>0.0030,0.0168,0.9832,0.0183</t>
+  </si>
+  <si>
+    <t>0.0685,0.0025,0.9641,0.0016</t>
+  </si>
+  <si>
+    <t>0.0072,0.0204,0.9791,0.0075</t>
+  </si>
+  <si>
+    <t>0.0100,0.0158,0.9762,0.0050</t>
+  </si>
+  <si>
+    <t>0.0281,0.0006,0.9850,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.0031,0.9958,0.0014</t>
+  </si>
+  <si>
+    <t>0.1261,0.0018,0.9018,0.0053</t>
+  </si>
+  <si>
+    <t>0.0576,0.0052,0.9526,0.0065</t>
+  </si>
+  <si>
+    <t>0.8404,0.0233,0.1463,0.0079</t>
+  </si>
+  <si>
+    <t>0.2063,0.0889,0.7303,0.0148</t>
+  </si>
+  <si>
+    <t>0.0524,0.0434,0.9147,0.0078</t>
+  </si>
+  <si>
+    <t>0.7650,0.0206,0.2181,0.0046</t>
+  </si>
+  <si>
+    <t>0.5972,0.0456,0.2500,0.1451</t>
+  </si>
+  <si>
+    <t>0.0989,0.0236,0.9018,0.0062</t>
+  </si>
+  <si>
+    <t>0.4937,0.6392,0.0023,0.0012</t>
+  </si>
+  <si>
+    <t>0.0292,0.9719,0.0026,0.0003</t>
+  </si>
+  <si>
+    <t>0.9902,0.0104,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.7088,0.3563,0.0041,0.0035</t>
+  </si>
+  <si>
+    <t>0.0418,0.9485,0.0015,0.0046</t>
+  </si>
+  <si>
+    <t>0.8876,0.0325,0.0668,0.0020</t>
+  </si>
+  <si>
+    <t>0.9762,0.0008,0.0107,0.0014</t>
+  </si>
+  <si>
+    <t>0.9365,0.0023,0.0036,0.0386</t>
+  </si>
+  <si>
+    <t>0.4947,0.0279,0.5657,0.0068</t>
+  </si>
+  <si>
+    <t>0.6475,0.0070,0.2920,0.0360</t>
+  </si>
+  <si>
+    <t>0.0364,0.0069,0.9493,0.0653</t>
+  </si>
+  <si>
+    <t>0.0663,0.0812,0.8422,0.0390</t>
+  </si>
+  <si>
+    <t>0.0491,0.0177,0.9538,0.0029</t>
+  </si>
+  <si>
+    <t>0.6657,0.0132,0.3665,0.0025</t>
+  </si>
+  <si>
+    <t>0.0545,0.5675,0.3786,0.0118</t>
+  </si>
+  <si>
+    <t>0.9948,0.0016,0.0003,0.0015</t>
+  </si>
+  <si>
+    <t>0.9972,0.0001,0.0001,0.0021</t>
+  </si>
+  <si>
+    <t>0.9906,0.0043,0.0005,0.0024</t>
+  </si>
+  <si>
+    <t>0.9921,0.0062,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9928,0.0026,0.0010,0.0015</t>
+  </si>
+  <si>
+    <t>0.9968,0.0007,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9929,0.0014,0.0006,0.0030</t>
+  </si>
+  <si>
+    <t>0.9980,0.0002,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.0109,0.2376,0.9728,0.0051</t>
+  </si>
+  <si>
+    <t>0.0220,0.0478,0.9600,0.0212</t>
+  </si>
+  <si>
+    <t>0.9700,0.0039,0.0068,0.0095</t>
+  </si>
+  <si>
+    <t>0.0048,0.0088,0.9932,0.0003</t>
+  </si>
+  <si>
+    <t>0.0038,0.0028,0.9880,0.0051</t>
+  </si>
+  <si>
+    <t>0.0096,0.0522,0.9668,0.0034</t>
+  </si>
+  <si>
+    <t>0.0096,0.0091,0.9912,0.0009</t>
+  </si>
+  <si>
+    <t>0.0089,0.0448,0.9657,0.0067</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0077,0.0135,0.9808,0.0019</t>
+  </si>
+  <si>
+    <t>0.0599,0.0173,0.9363,0.0084</t>
+  </si>
+  <si>
+    <t>0.7581,0.0001,0.2701,0.0020</t>
+  </si>
+  <si>
+    <t>0.2414,0.0040,0.7002,0.0352</t>
+  </si>
+  <si>
+    <t>0.9893,0.0005,0.0046,0.0004</t>
+  </si>
+  <si>
+    <t>0.9831,0.0046,0.0017,0.0060</t>
+  </si>
+  <si>
+    <t>0.9977,0.0008,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9977,0.0004,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9916,0.0050,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.9963,0.0004,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9924,0.0019,0.0017,0.0011</t>
+  </si>
+  <si>
+    <t>0.9949,0.0026,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9955,0.0013,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.0081,0.0731,0.9480,0.0032</t>
+  </si>
+  <si>
+    <t>0.0100,0.0809,0.9759,0.0012</t>
+  </si>
+  <si>
+    <t>0.0097,0.0069,0.9825,0.0056</t>
+  </si>
+  <si>
+    <t>0.0599,0.0531,0.8181,0.0096</t>
+  </si>
+  <si>
+    <t>0.0069,0.0001,0.9970,0.0001</t>
+  </si>
+  <si>
+    <t>0.0574,0.0110,0.8419,0.0796</t>
+  </si>
+  <si>
+    <t>0.0117,0.0202,0.9657,0.0181</t>
+  </si>
+  <si>
+    <t>0.7151,0.0084,0.2471,0.0201</t>
+  </si>
+  <si>
+    <t>0.9723,0.0002,0.0005,0.0388</t>
+  </si>
+  <si>
+    <t>0.0131,0.0079,0.0004,0.9929</t>
+  </si>
+  <si>
+    <t>0.0157,0.0019,0.0009,0.9923</t>
+  </si>
+  <si>
+    <t>0.0017,0.0004,0.0003,0.9990</t>
+  </si>
+  <si>
+    <t>0.0030,0.0001,0.0001,0.9990</t>
+  </si>
+  <si>
+    <t>0.8515,0.0056,0.0250,0.1230</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2273,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,10 +2326,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2483,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,10 +2522,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,10 +2970,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3141,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3166,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3572,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3673,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3698,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3855,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3922,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3939,7 @@
         <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4006,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,10 +4216,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4387,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4709,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>259</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4902,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5199,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>259</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
